--- a/wildberries_ru/filtered_items.xlsx
+++ b/wildberries_ru/filtered_items.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,1089 @@
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>images</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/303239532/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>303239532</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Пальто без подклада</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Магазин одежды бохо</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/61696</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>oversize 50-54, oversize 56-60, oversize 62-66, oversize 46-48</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>209</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Демисезонное женское пальто без подклада от milidi – идеальный выбор для создания стильных образов весна-осень 2026. Модель выполнена из высококачественной вареной и валяной шерсти, благодаря чему изделие обладает отличными тепловыми свойствами и сохраняет внешний вид на протяжении долгого времени. Дизайнерская модель легкого женского пальто без подклада подчеркивается английским воротником и универсальным синим цветом, что делает это женское пальто из лодена не только практичным, но и невероятно модным решением для любого случая.
+Кардиган женский удлиненный представлен в размере оверсайз, что позволяет носить его девушкам и женщинам plus size, а также беременным – изделие не сковывает движений и подходит для больших размеров и полных. Летнее модное пальто milidi гармонично сочетается с вещами в стиле бохо, классика и премиум.
+Полупальто milidi – это базовая вещь для гардероба, подходящая для создания уютного и теплого образа. Преимущества: натуральная шерсть, современный дизайн с накладными карманами, универсальность (весна-осень). 
+Бренд MILIDI имеет свое производство в России,  что позволяет нам контролировать высокое качество одежды больших размеров!</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 80%; Вискоза 20%
+Цвет:  темно-синий; синий; синий космос; черно-синий; ночной синий
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пуговицы; без пояса
+Рост модели на фото:  173 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  90-63-93
+Размер на модели:  50-54
+Утеплитель:  без утеплителя
+Температурный режим:  от +5 °C до +15 °C
+Материал подкладки:  без подкладки
+Покрой:  прямой
+Тип карманов:  накладные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Мех опушки/отделки:  без меха
+Декоративные элементы:  без элементов; однотонное; для полных
+Особенности модели:  тонкое; легкое; Кардиган пальто женский больших размеров
+Уход за вещами:  деликатная стирка в режиме "шерсть" при температуре не выше 30 градусов; без отжима; сушка только в горизонтальном положении при естественных условиях
+Комплектация:  Пальто демисезонное длинное - 1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/1.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/2.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/3.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/4.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/5.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/6.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/7.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/8.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/9.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/10.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/11.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/12.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/13.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/14.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/15.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/16.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/17.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/18.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/19.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/20.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/197268380/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>197268380</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Пальто зимнее длинное теплое</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8002</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Eurydike</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/3971567</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>46, 48, 50, 52, 54, 44, 56, 58</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>66</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Данное пальто представляет собой модный и практичный вариант для осеннего и зимнего сезонов, идеально подходящий для девушек с фигурами размером 48-58. Высококачественная мягкая ткань, использованная при его выполнении, обеспечивает комфорт и уют в прохладные дни. Этот дизайнерский предмет одежды с удлиненным прямым фасоном подчеркивает индивидуальность, а его серый цвет и классический дизайн добавляют вещи актуальности в любой коллекции.
+Модель оснащена английским воротником,  закрывающимся и защищающим от холодного воздуха, и прорезными накладными скошенными карманами, добавляющими функциональность. Многослойные элементы конструкции делают его особенно удобным для носки, позволяя использовать его как в деловом, так и в повседневном стиле. В сочетании с высокими сапогами или кроссовками, этот вариант станет отличным решением для прогулок и активного отдыха.
+В процессе создания этого изделия присутствуют натуральные материалы, которые обеспечивают должный уход и долговечность. Пальто имеет утеплитель,в составе которого - 100% шерсть, он защищает от низких температур, что делает его идеальным для межсезонья, позволяя  его носить в еврозиму. Данная верхняя одежда выделяется на фоне других благодаря своему уникальному дизайну и трендовому виду. 
+С таким базовым изделием легко комбинировать другие элементы гардероба, создавая завершенный образ актуальный в течение всего зимнего сезона.  Эта модель станет незаменимой частью вашего гардероба, добавляя в него стиль и уют. Подчеркните свою женственность с этой модной вещью,  соответствующей самым последним трендам и требованиям.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Состав:  50% шерсть, 30% вискоза, 20% поливискоза
+Цвет:  серо-бежевый; серый; серый меланж; бежевый; серо-бежевый светлый
+Сезон:  зима
+Вид застежки:  пуговицы
+Рост модели на фото:  175 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  84-64-93
+Размер на модели:  46
+Утеплитель:  шерсть
+Плотность синтетического утеплителя:  180 г/кв.м
+Температурный режим:  от -10 до +5
+Материал подкладки:  полиэстер; шерстепон
+Покрой:  свободный
+Тип карманов:  накладные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Мех опушки/отделки:  без меха
+Декоративные элементы:  без элементов
+Особенности модели:  ветрозащита; дышащий материал; теплое
+Конструктивные элементы:  свободный крой
+Пол:  Женский
+Уход за вещами:  допускается отпаривание; деликатная химическая чистка
+Комплектация:  пояс; пальто
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/1.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/2.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/3.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/4.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/5.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/6.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/7.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/8.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/9.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/10.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/11.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/12.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/13.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/14.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/15.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/16.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/17.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/18.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/19.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/446834586/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>446834586</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное оверсайз короткое</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9303</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CORESSI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/26796</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52, 54</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>291</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Окунитесь в стиль и комфорт, выбирая женское пальто для сезона весна–осень. Это короткое демисезонное пальто станет практичным и стильным решением для повседневной носки в прохладную погоду. Модель сочетает актуальный дизайн и функциональность, позволяя чувствовать себя уютно и уверенно каждый день.
+Двубортное твидовое пальто прямого кроя выполнено с английским воротником, декоративными погонами и патами на рукавах. Застёжка на пуговицах формирует аккуратный силуэт и подчёркивает классические линии. Длина изделия по спинке — 63,5 см, длина рукава от линии втачивания воротника — 75 см, что делает модель удобной и универсальной.
+Тёплое укороченное пальто создаёт ощущение уюта и защищает от прохлады в межсезонье. Натуральная ворсовая ткань с высоким содержанием шерсти помогает сохранять комфортное тепло, а кашемировое ощущение мягкости делает изделие особенно приятным в носке. Такое шерстяное полупальто подойдёт для весенних и осенних дней.
+Модель гармонично вписывается как в кэжуал-образы, так и в офисную классику. Коричневый цвет легко сочетается с базовым гардеробом. Это пальто универсальный выбор для автоледи,оптимальная длина не сковывает движения и обеспечивает комфорт за рулём.
+Изделие привлекает внимание винтажным настроением, которое создаётся за счёт прямого кроя, выразительных деталей и благородного оттенка. Стиль подчёркивает индивидуальность и соответствует модным тенденциям 2026 года. Размерный ряд делает модель подходящей как для женщин, так и для подростков.
+Ткань имеет ворсистую фактуру благодаря большому проценту шерсти, поэтому возможно прилипание волокон, шерсти животных и пыли. Материал не скатывается, сохраняет форму и цвет. В процессе носки ворс может подниматься — рекомендуется очищать поверхность липким роликом и велюровой щёткой по направлению ворса.
+Вся продукция бренда CORESSI производится в России, отшивается на современном швейном оборудовании и проходит строгий контроль качества. Будем признательны за оставленный отзыв. Приятных покупок!
+</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 57%; вискоза 36%; полиэстер 7%
+Цвет:  коричневый
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  167 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  89-66-96
+Размер на модели:  44
+Утеплитель:  без утеплителя
+Температурный режим:  от 0 °C до +15 °C
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  прорезные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  декоративная отстрочка; погоны; пуговицы
+Особенности модели:  ветрозащита; оверсайз; двубортная
+Уход за вещами:  деликатная химическая чистка; допускается отпаривание
+Комплектация:  Пальто - 1 шт; Упаковочная сумка-чемодан
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/1.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/2.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/3.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/4.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/5.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/6.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/7.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/8.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/9.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/10.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/11.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/12.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/13.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/14.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/15.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/16.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/17.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/26800702/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>26800702</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное большие размеры</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8002</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Primadonna</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/47927</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>48, 50, 52, 54, 60</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Женское пальто бренда PDONNA выполнено из натуральной шерсти, свободного кроя. Модель имеет застёжку -пуговицы, воротник- стойка, карманы прорезные с листочкой. Эта модель подчеркнёт Вашу фигуру и создаст элегантный образ. Пальто прекрасно сочетается как с классическими брюками и юбкой, так и с вечернем платьем. При заказе обязательно сверьтесь с нашей таблицей размеров.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер; шерсть; текстиль
+Цвет:  коралловый
+Сезон:  демисезон
+Вид застежки:  пуговицы; кнопки
+Утеплитель:  полиэстер
+Температурный режим:  +5 до +15
+Материал подкладки:  полиэстер
+Покрой:  свободный
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  без элементов
+Особенности модели:  износостойкость
+Конструктивные элементы:  воротник
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  пальто женское демисезонное -1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbbasket.ru/vol268/part26800/26800702/images/big/1.webp, https://basket-02.wbbasket.ru/vol268/part26800/26800702/images/big/2.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/250798523/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>250798523</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное длинное оверсайз</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3411</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LadiesGard</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1196458</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>93</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Пальто женское демисезонное длинное оверсайз – базовый предмет гардероба и тренд сезона осень-зима 2024-2025. Удлиненная драповая модель на запах с двубортным дизайном подчеркнет элегантность, а прямой свободный oversize крой подойдет девушкам, девочкам подросткам в школу и полным plus size. Кашемировое с английским воротником на любую фигуру и рост, высоким и невысоким. Оно легкое и приятное на ощупь, оснащено пуговицами и поясом для дополнительного комфорта и поддержания формы, по желанию вы сможете создать приталенный силуэт. Универсальное широкое шерстяное осеннее пальтишко со спущенными большими реглан плечами обеспечивают свободу движений. Оверсайз крой создаст неповторимый образ в корейском стиле y2k. Красивый разрез со спины must-have для каждой модницы! Вместительные карманы с клапаном добавляют удобство и практичность. Верхняя одежда для вечерних прогулок в межсезонье, на весну осень. Классическое теплое серое зимнее пальто выполнено из высококачественной шерсти с подкладом из полиэстера, не тяжелое и комфортное в повседневной носке. Идеально для создания многослойных образов на каждый день - от офисного до спортивного и молодежного городского casual и тематической фотосессии как в пинтерест (Pinterest).</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 55%; акрил 40%; полиэстер 5%
+Цвет:  серый; серый меланж; натуральный серый
+Сезон:  демисезон
+Размер на модели:  42
+Рост модели на фото:  168 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  80-60-90
+Утеплитель:  нет
+Температурный режим:  от -5 °C до +10 °C
+Материал подкладки:  полиэстер 100%
+Страна производства:  Россия
+Вид застежки:  пуговицы; пояс
+Особенности модели:  двубортное пальто из шерсти; износостойкость; с широкими плечами
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  шлица; пояс; oversize
+Тип карманов:  с клапаном; врезной; листочка
+Конструктивные элементы:  шлевки
+Пол:  Женский
+Тип рукава:  длинные
+Комплектация:  Пальто женское - 1 шт., пояс - 1 шт.
+Покрой:  прямой
+Уход за вещами:  деликатная химическая чистка; стирка запрещена</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/1.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/2.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/3.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/4.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/5.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/6.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/7.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/8.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/9.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/10.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/11.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/12.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/13.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/14.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/15.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/16.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/17.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/18.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/19.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/26800674/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>26800674</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное большие размеры</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9336</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Primadonna</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/47927</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>46, 48, 50, 52, 54, 56, 58, 60</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Женское пальто бренда PDONNA выполнено из натуральной шерсти, полуприталенного силуэта. Пальто имеет застёжку - кнопки, воротник- отложной, карманы прорезные по линии шва. Эта модель подчеркнёт Вашу фигуру и создаст элегантный образ. Пальто прекрасно сочетается как с классическими брюками и юбкой, так и с повседневным стилем. При заказе обязательно сверьтесь с нашей таблицей размеров.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер; шерсть; текстиль
+Цвет:  шоколадный
+Сезон:  демисезон
+Вид застежки:  кнопки
+Утеплитель:  полиэстер
+Температурный режим:  +5 до +15
+Материал подкладки:  полиэстер
+Покрой:  приталенный
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  без элементов
+Особенности модели:  износостойкость
+Конструктивные элементы:  воротник
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  пальто женское -1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbbasket.ru/vol268/part26800/26800674/images/big/1.webp, https://basket-02.wbbasket.ru/vol268/part26800/26800674/images/big/2.webp, https://basket-02.wbbasket.ru/vol268/part26800/26800674/images/big/3.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/26800613/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26800613</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное большие размеры</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8336</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Primadonna</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/47927</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>46, 48, 50, 52, 56, 60</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Женское пальто бренда PDONNA выполнено из натуральной шерсти, полуприталенного силуэта. Модель имеет застёжку -пуговицы, воротник- английский, карманы прорезные с листочкой. Пальто прекрасно сочетается как с классическими брюками и юбкой, так и с вечерним платьем . При заказе обязательно сверьтесь с нашей таблицей размеров.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер; шерсть; текстиль
+Цвет:  черный
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Утеплитель:  полиэстер
+Температурный режим:  +5 до +15
+Материал подкладки:  полиэстер
+Покрой:  приталенный
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пояс
+Особенности модели:  износостойкость
+Конструктивные элементы:  воротник
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  Пальто женское демисезонное -1шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbbasket.ru/vol268/part26800/26800613/images/big/1.webp, https://basket-02.wbbasket.ru/vol268/part26800/26800613/images/big/2.webp, https://basket-02.wbbasket.ru/vol268/part26800/26800613/images/big/3.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/198381803/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>198381803</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Пальто короткое</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9229</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Filigreen</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1418640</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>M-L, S-M</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Пальто женское демисезонное укороченное. Подойдет: в офис, в школу, на работу или на прогулку с друзьями. Свободный фасон и продуманный крой делают модель очень комфортной в носке. Придаст элегантности любому образу, а короткая длина подчеркнет ноги и добавить образу легкости. Оно выполнено из высококачественной шерсти с добавлением вискозы, что обеспечивает натуральную теплоизоляцию. Наше пальто - это настоящий стильный и модный предмет гардероба, который подчеркнет вашу индивидуальность. Уникальный разработанный нами дизайн - придаст неповторимость вашему образу. Уникальный крой на спине, эксклюзивная итальянская фурнитура. Мягкий материал, не деформируется при стирке. Подкладка выполнена из полиэстера. Драповая фактура материала смотрится стильно и дорого. Удобные карманы, с кожаными ставками придают образу женственности. Закажите люксовое, короткое пальто прямо сейчас и почувствуйте себя настоящей королевой. Filigreen - это профессиональный пошив и высокое качество.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер 90%, шерсть 10%
+Цвет:  зеленый; изумрудно-зеленый; изумрудный
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  164 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  84-60-90
+Размер на модели:  42-44
+Плотность синтетического утеплителя:  100 г/кв.м
+Температурный режим:  от +10 °C до -5 °C
+Покрой:  оверсайз
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  кожаные вставки
+Особенности модели:  дышащий материал
+Конструктивные элементы:  вставки
+Пол:  Женский
+Уход за вещами:  химическая чистка
+Комплектация:  Пальто - 1 шт.
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>https://basket-13.wbbasket.ru/vol1983/part198381/198381803/images/big/1.webp, https://basket-13.wbbasket.ru/vol1983/part198381/198381803/images/big/2.webp, https://basket-13.wbbasket.ru/vol1983/part198381/198381803/images/big/3.webp, https://basket-13.wbbasket.ru/vol1983/part198381/198381803/images/big/4.webp, https://basket-13.wbbasket.ru/vol1983/part198381/198381803/images/big/5.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/317871295/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>317871295</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Пальто весеннее длинное</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6303</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ETIKA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/468951</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Стильное женское драповое пальто, которое станет настоящим хитом сезона весна-осень 2026! Это удлиненное пальто оверсайз тренд 2026 для девушек идеально подойдет для прохладных дней, обеспечивая отличный комфорт и тепло благодаря высококачественным материалам, таким как натуральная шерсть.
+Данное молодежное женское весенне-осеннее пальто станет вашим верным спутником в повседневной жизни и на особых событиях. Его универсальный дизайн позволяет комбинировать его с различными нарядами, а пояс, который позволяет подчеркнуть талию, добавляет элегантности в образ. Английский воротник придаст вашему стилю изысканность и утонченный вкус.
+Весеннее пальто на запах  для женщин до колен, что подчеркивает гармоничное сочетание стиля и практичности. Благодаря шлевкам для пояса, голубое пальто женское весна-осень длинное классика всегда будет выглядеть безупречно, а теплота шерсти защитит вас от холодной осени и прохладной весны.
+Мы предлагаем женскую одежду с большим выбором размеров, включая большие размеры, что делает эту стильную вещь доступной для всех модниц, в том числе и вещью для беременных. Эта элегантное кашемировое женское пальто прекрасно подходит для демисезонного периода, а материалы премиального качества обеспечивают устойчивость к износу.
+Станьте обладательницей женственной одежды-актуального демисезонного пальто кашемир, которое сочетает в себе тепло, уют и неповторимый шарм. Не упустите возможность обновить свой гардероб с помощью пальто весеннего классического.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; вискоза; полиэстер
+Цвет:  кофейный; коричневый меланж; бледно-коричневый
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пояс; кнопки
+Рост модели на фото:  175 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  82-63-91
+Размер на модели:  42
+Температурный режим:  от 0 °C до +15 °C
+Материал подкладки:  поливискоза
+Покрой:  полуприлегающий
+Тип карманов:  прорезные
+Особенности модели:  со шлицей; однобортная
+Уход за вещами:  химическая чистка
+Комплектация:  плечики; пояс; пальто
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/1.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/2.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/3.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/4.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/5.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/6.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/7.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/8.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/9.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/822687844/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>822687844</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Пальто</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/350185895</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Прекрасное зимнее пальто под любой образ и стиль. Состояние отличное, носила редко, хранится в чехле в шкафу.  Маркировка 44, но идёт на 42.  Мех натуральный, не лезет, пышный.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Состав:  Эластан 5%; вискоза 15%; шерсть 80%
+Цвет:  синий
+Сезон:  зима
+Вид застежки:  пуговицы
+Утеплитель:  ватин
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  съемная опушка
+Конструктивные элементы:  нет
+Пол:  Женский
+Уход за вещами:  бережная стирка при 30 градусах
+Комплектация:  пальто; пояс
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>https://basket-37.wbbasket.ru/vol8226/part822687/822687844/images/big/1.webp, https://basket-37.wbbasket.ru/vol8226/part822687/822687844/images/big/2.webp, https://basket-37.wbbasket.ru/vol8226/part822687/822687844/images/big/3.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/182658371/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>182658371</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Пальто женское зимнее оверсайз теплое укороченное</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6113</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>EURYDIKE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/23312</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>48, 50, 52, 54, 56</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Модное и укороченное зимнее пальто из качественной ткани, на большие размеры, выгодно и приятно, выделит  Вас из общей массы, особенно холодной и морозной зимой. Молодежная модель сшита из мягкой, ворстистой, шерстяной ткани, прошедшей специальную тепловую обработку, что бы не терять форму и вид, при носке и попаданию под дождь или снег. Такая верхняя женская одежда, позволит вам  чувствовать себя максимально комфортнов и удобно в зимний и демисезонный период, холодной осенью и ранней весной.  Драповые пальто из тканей под искуственные шубы, тедди и чебурашки, являются трендом и очень практичны в носке. Производство Россия. Размеры с 48 по 56. В комплекте есть пояс, с помощью которого, можно приталить пальто и подчеркнуть фигуру. Удобный спущенный рукав, обеспечит Вам  свободу движения и позволит одевать под стильное пальто любую одежду. Утеплитель стеганный шерстепон из 100% натуральной шерсти. Аккуратный и маленький английский воротник надежно прикроет вашу шею от холода. Стильная классическая модель халат, идеально подойдет тем, кто за рулем и тем, кто не любит длинные и тяжелые утепленные пальто.  Так же модель можно одеть на свадьбы, дни рождения и другие торжественные мероприятия. Дизайнерское пальто подойдет как женщинам, так и молодым девушкам, а так же беременным, будущим и молодым мамам. Его Вы можете одевать на выход, на работу или в офис, а так же для прогулок с друзьями. Вам в нем всегда будет комфортно и уютно, а так же тепло и удобно. Короткая, классическая модель прекрасно подойдет, на любой рост, на средний, низкий и на высокий. Сейчас брендовая модель учавствует в акции, её можно приобрести по выгодной, распродажной и низкой цене. Оно станет прекрасным подарком вашим любимым женщинам в Новогодние, Рожденственские и другие праздники, а так же дни рождения. </t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Состав:  50 шерсть, 30 вискоза, 20 полиэстер
+Цвет:  светло-бежевый
+Сезон:  зима
+Размер на модели:  48
+Рост модели на фото:  168 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  96-70-94
+Утеплитель:  шерстепон
+Температурный режим:  от -15 до +10
+Плотность синтетического утеплителя:  180 г/кв.м
+Материал подкладки:  полиэстер; шерстепон
+Страна производства:  Россия
+Вид застежки:  кнопки; пуговицы
+Особенности модели:  для невысоких
+Опции капюшона:  без капюшона
+Длина изделия по спинке:  90 см
+Опции опушки:  без опушки
+Декоративные элементы:  молодежное; зима; шубка
+Тип карманов:  прорезные
+Конструктивные элементы:  оверсайз
+Пол:  Женский
+Тип рукава:  длинные
+Комплектация:  пояс; верхняя одежда; для женщин; шуба; Альпака; пальто
+Покрой:  оверсайз
+Уход за вещами:  деликатная химическая чистка; допускается отпаривание</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/1.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/2.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/3.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/4.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/5.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/6.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/7.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/8.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/9.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/10.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/11.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/12.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/13.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/14.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/15.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/16.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/17.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/18.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/19.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/20.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/21.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/543334996/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>543334996</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Пальто утеплённое шерстяное с воротником стойкой</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8560</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CORESSI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/26796</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52, 54</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>464</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пальто женское весна-осень CORESSI (КОРЕССИ) — стильная и практичная модель для сезона 2026 года. Базовое женское пальто легко вписывается в повседневный и деловой гардероб.
+Женское короткое пальто на весну и осень подходит для повседневной носки, офиса и городских образов. Утеплённая шерстяная демисезонная модель обеспечивает комфорт в прохладную погоду и межсезонье.
+Состав: шерсть — 57%, вискоза — 36%, полиэстер — 7%.
+Длина по спинке — 63 см. Длина рукава — 63,5 см.
+Компактная длина делает короткое пальто особенно удобным для поездок за рулём и активного ритма города. Пальто женское автоледи комфортно при движении и не сковывает посадку за рулём. Изделие выполнено из ткани с высоким содержанием натуральной шерсти. Плотная пальтовая ткань мягкая, приятная к телу и хорошо держит форму.
+Внутри используется современный утеплитель TermoFinn (термофин), созданный по технологии ультратонкого микроволокна. Он лёгкий, не деформируется, не даёт усадки, его структура помогает сохранять естественное тепло и поддерживать комфортный температурный баланс в течение дня, адаптируясь к переменчивой осенней и весенней погоде.
+Однобортный крой и кнопки формируют аккуратный силуэт, воротник-стойка защищает от ветра. Глубокие карманы с листочкой добавляют практичности и подчёркивают продуманный дизайн.
+Цвет — черный (глубокий черный): базовый оттенок, который легко сочетается с офисными и повседневными комплектами. Черное женское пальто выглядит сдержанно и современно. Укороченное пальто для женщин остаётся практичным выбором на каждый день.
+Ворсовая поверхность ткани обусловлена высоким содержанием шерсти. Уход простой: используйте липкий ролик или велюровую щётку по направлению ворса, чтобы поддерживать аккуратный вид ткани.
+Пальто отшивается в России на современном оборудовании и проходит строгий контроль качества. Классическое демисезонное пальто подходит для ранней весны и прохладной осени, а также может использоваться как вариант для еврозимы и мягкой теплой зимы.
+</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; вискоза; полиэстер
+Цвет:  черный; глубокий черный
+Пол:  Женский
+Сезон:  демисезон
+Вид застежки:  кнопки
+Рост модели на фото:  164 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  83-60-89
+Размер на модели:  42
+Утеплитель:  термофин
+Плотность синтетического утеплителя:  100 г/кв.м
+Температурный режим:  от -5°C до +15°С
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  застежка на кнопках; глубокие карманы с листочкой; Ворсовая ткань
+Особенности модели:  однобортная; ветрозащита; износостойкость
+Уход за вещами:  деликатная химическая чистка; допускается отпаривание
+Комплектация:  Пальто - 1 шт; упаковочная сумка чемодан
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/1.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/2.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/3.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/4.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/5.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/6.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/7.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/8.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/9.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/10.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/11.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/12.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/13.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/14.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/15.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/256159109/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>256159109</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Пальто утепленное с мехом</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8757</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ABRIGO COLLECTION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4185520</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>42, 46</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Женское зимнее пальто, выполненное полуприталенным кроем, выгодно подчеркивает талию и зрительно добавляет роста. Длинное женское пальто изготовлено из качественных материалов: шерсть с добавлением вискозы и эластана с меховой опушкой, защищающих от пониженных температур до -15 С.Не рекомендуется сушить женское пальто с помощью барабанной сушки. Качественные материалы обеспечивают длительный срок носки. Разнообразие расцветок позволяет подобрать вариант под конкретный стиль. Материал устойчив к образованию катышек (особенно в области подмышек от длительной носки сумки). Подклад из полиэстера и меховой воротник надежно защищают от проникновения ветра. В ассортименте модели для полных и стройных, все зимние пальто имеют длину до колена и прямой полуприталенный крой. Женское пальто больших размеров изготовлено с учетом особенностей фигуры. Качественный пошив и натуральная шерсть обеспечивают комфорт в зимнюю погоду и надежно защищают от холода.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть-75%; вискоза-20%; эластан-5%
+Цвет:  черный; серый
+Сезон:  зима
+Размер на модели:  44
+Рост модели на фото:  174 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  92-66-94
+Утеплитель:  шерсть
+Материал подкладки:  полиэстер
+Температурный режим:  от 0 °C до -14 °C
+Вид застежки:  пуговица
+Воротник:  классический
+Опции капюшона:  без капюшона
+Опции опушки:  съемная опушка
+Тип карманов:  прорезные
+Особенности модели:  ветрозащита
+Пол:  Женский
+Уход за вещами:  барабанная сушка запрещена
+Комплектация:  Пальто женское зимнее с поясом-1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2561/part256159/256159109/images/big/1.webp, https://basket-16.wbbasket.ru/vol2561/part256159/256159109/images/big/2.webp, https://basket-16.wbbasket.ru/vol2561/part256159/256159109/images/big/3.webp, https://basket-16.wbbasket.ru/vol2561/part256159/256159109/images/big/4.webp, https://basket-16.wbbasket.ru/vol2561/part256159/256159109/images/big/5.webp</t>
         </is>
       </c>
     </row>
